--- a/data/trans_dic/P1410-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1410-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,97</t>
+          <t>2,89; 7,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,3</t>
+          <t>1,53; 6,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,53</t>
+          <t>1,4; 5,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,13</t>
+          <t>3,09; 7,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,13</t>
+          <t>0,41; 4,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,4</t>
+          <t>2,21; 7,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,11</t>
+          <t>1,95; 7,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,11</t>
+          <t>1,81; 4,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,03</t>
+          <t>1,96; 5,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,65</t>
+          <t>2,37; 5,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,24</t>
+          <t>2,13; 5,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,46</t>
+          <t>2,8; 5,42</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 9,11</t>
+          <t>4,26; 8,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,99</t>
+          <t>1,79; 5,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,91</t>
+          <t>2,47; 5,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,03</t>
+          <t>3,58; 7,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,04</t>
+          <t>3,94; 7,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,58</t>
+          <t>2,59; 6,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,94</t>
+          <t>3,28; 7,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,05</t>
+          <t>3,12; 5,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,7</t>
+          <t>4,63; 7,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,14</t>
+          <t>2,62; 5,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,06</t>
+          <t>3,33; 5,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,15</t>
+          <t>3,68; 6,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,12</t>
+          <t>2,07; 6,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,25</t>
+          <t>2,85; 8,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 7,94</t>
+          <t>3,14; 7,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,94</t>
+          <t>4,06; 8,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,45</t>
+          <t>1,88; 5,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 8,78</t>
+          <t>3,69; 8,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,21</t>
+          <t>1,08; 5,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 8,46</t>
+          <t>4,65; 8,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,48</t>
+          <t>2,57; 5,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,52</t>
+          <t>3,84; 7,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,6</t>
+          <t>2,53; 5,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 7,95</t>
+          <t>4,94; 7,85</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,31</t>
+          <t>1,77; 5,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,78</t>
+          <t>3,84; 8,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,31</t>
+          <t>2,26; 6,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,84</t>
+          <t>3,9; 8,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,16</t>
+          <t>1,08; 4,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,58</t>
+          <t>2,86; 7,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 13,03</t>
+          <t>6,32; 12,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,57</t>
+          <t>2,74; 6,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,04</t>
+          <t>1,66; 3,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,06</t>
+          <t>3,74; 6,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,81</t>
+          <t>4,85; 8,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,13</t>
+          <t>3,59; 6,77</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,61</t>
+          <t>2,63; 8,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,87</t>
+          <t>1,11; 6,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,81</t>
+          <t>0,76; 4,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,86</t>
+          <t>1,8; 5,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 7,68</t>
+          <t>1,6; 7,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 9,03</t>
+          <t>2,75; 9,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,96</t>
+          <t>0,43; 4,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,1</t>
+          <t>1,99; 5,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,96</t>
+          <t>2,57; 6,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,59</t>
+          <t>2,45; 6,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,67</t>
+          <t>0,9; 3,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,57</t>
+          <t>2,23; 4,69</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,34</t>
+          <t>2,78; 7,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,03</t>
+          <t>2,73; 8,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,32</t>
+          <t>1,06; 5,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,86</t>
+          <t>5,35; 10,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,33</t>
+          <t>0,75; 4,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,57</t>
+          <t>3,89; 10,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,16</t>
+          <t>3,13; 9,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,83</t>
+          <t>4,64; 8,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,32</t>
+          <t>2,16; 5,51</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,03</t>
+          <t>4,11; 8,13</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,05</t>
+          <t>2,45; 6,15</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,95</t>
+          <t>5,5; 8,75</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,85</t>
+          <t>2,13; 4,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,45</t>
+          <t>3,17; 6,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,0</t>
+          <t>2,18; 5,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,73; 9,46</t>
+          <t>4,62; 8,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,82</t>
+          <t>2,83; 6,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,29</t>
+          <t>1,69; 4,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,92</t>
+          <t>2,46; 5,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,69</t>
+          <t>4,14; 6,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,01</t>
+          <t>2,74; 4,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,75</t>
+          <t>2,74; 4,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,0</t>
+          <t>2,68; 4,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,39</t>
+          <t>4,84; 7,33</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,74</t>
+          <t>3,65; 6,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,56</t>
+          <t>1,41; 3,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,09</t>
+          <t>3,1; 6,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,68</t>
+          <t>3,01; 5,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,12</t>
+          <t>3,08; 6,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,59</t>
+          <t>2,08; 4,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,54</t>
+          <t>2,57; 5,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,0</t>
+          <t>2,06; 3,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,7; 5,88</t>
+          <t>3,64; 5,72</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,64</t>
+          <t>1,94; 3,62</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,27</t>
+          <t>3,28; 5,25</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,85</t>
+          <t>2,74; 4,3</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,34</t>
+          <t>3,91; 5,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,49</t>
+          <t>3,24; 4,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,42</t>
+          <t>3,15; 4,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,9</t>
+          <t>4,71; 6,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,46</t>
+          <t>3,15; 4,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,92</t>
+          <t>3,54; 4,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,3</t>
+          <t>3,8; 5,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,71</t>
+          <t>3,84; 4,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,66</t>
+          <t>3,71; 4,65</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,56; 4,51</t>
+          <t>3,58; 4,52</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,68; 4,65</t>
+          <t>3,68; 4,68</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,11</t>
+          <t>4,46; 5,35</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>25389</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8024; 21750</t>
+          <t>7899; 21705</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4771; 18558</t>
+          <t>4519; 17784</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4112; 16260</t>
+          <t>4127; 16897</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8383; 22196</t>
+          <t>9864; 23307</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1072; 10766</t>
+          <t>1074; 10456</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6965; 21268</t>
+          <t>6354; 21294</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5470; 20535</t>
+          <t>5643; 20954</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6088; 17696</t>
+          <t>5730; 15445</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10884; 26866</t>
+          <t>10460; 27329</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14088; 32862</t>
+          <t>13793; 32600</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12209; 30500</t>
+          <t>12430; 30076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16892; 32844</t>
+          <t>17802; 34385</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28207</t>
+          <t>28566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>23538</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50224</t>
+          <t>52104</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21370; 44933</t>
+          <t>21022; 42523</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9208; 25239</t>
+          <t>9028; 26072</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13124; 29719</t>
+          <t>12430; 29464</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18256; 41459</t>
+          <t>18895; 41389</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20117; 40524</t>
+          <t>19875; 40230</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14839; 34474</t>
+          <t>13566; 33228</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16644; 36294</t>
+          <t>17135; 37591</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15846; 31091</t>
+          <t>17002; 32283</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44761; 76819</t>
+          <t>46208; 74831</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26548; 52919</t>
+          <t>27012; 51908</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34251; 62181</t>
+          <t>34127; 60486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37272; 63331</t>
+          <t>39471; 66129</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>19206</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>22983</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>42189</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7491; 22696</t>
+          <t>6595; 21340</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9391; 26741</t>
+          <t>9224; 26450</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10694; 25293</t>
+          <t>9989; 25445</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13287; 28256</t>
+          <t>12835; 27363</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6829; 21628</t>
+          <t>6291; 20013</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12563; 29932</t>
+          <t>12600; 29780</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3712; 17517</t>
+          <t>3643; 17739</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16365; 29530</t>
+          <t>16585; 30484</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16093; 35858</t>
+          <t>16790; 35183</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25416; 50008</t>
+          <t>25556; 49623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16360; 36663</t>
+          <t>16564; 36268</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33143; 52869</t>
+          <t>33206; 52793</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35120</t>
+          <t>38571</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6113; 19037</t>
+          <t>6343; 18795</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14616; 32834</t>
+          <t>14360; 33250</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8279; 23334</t>
+          <t>8371; 22277</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12605; 27621</t>
+          <t>14539; 29975</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3167; 15442</t>
+          <t>3994; 15665</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11456; 29492</t>
+          <t>11118; 27860</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24955; 50456</t>
+          <t>24471; 50222</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9450; 26483</t>
+          <t>11571; 29381</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12591; 29489</t>
+          <t>12085; 27433</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29703; 53865</t>
+          <t>28564; 53109</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36578; 66699</t>
+          <t>36709; 66689</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23476; 48338</t>
+          <t>28569; 53864</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>14095</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5213; 17511</t>
+          <t>5340; 17000</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2287; 14603</t>
+          <t>2357; 13303</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1782; 10154</t>
+          <t>1614; 9734</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3083; 10465</t>
+          <t>3694; 11509</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3457; 15943</t>
+          <t>3316; 15585</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6042; 19832</t>
+          <t>6029; 19935</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1107; 10845</t>
+          <t>939; 9666</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3857; 10601</t>
+          <t>4514; 11460</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11188; 28591</t>
+          <t>10573; 28228</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10795; 28463</t>
+          <t>10607; 27694</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4284; 15785</t>
+          <t>3870; 15682</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8968; 17671</t>
+          <t>9640; 20269</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20943</t>
+          <t>20545</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16627</t>
+          <t>16873</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37569</t>
+          <t>37417</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7804; 22594</t>
+          <t>7516; 21484</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7458; 21991</t>
+          <t>7474; 22129</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2677; 13990</t>
+          <t>2798; 14617</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15314; 29286</t>
+          <t>14486; 28370</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2100; 12048</t>
+          <t>2096; 12785</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11902; 29394</t>
+          <t>10830; 29003</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8764; 25010</t>
+          <t>8536; 25819</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12046; 22647</t>
+          <t>12197; 23011</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12133; 29207</t>
+          <t>11875; 30265</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22272; 44337</t>
+          <t>22666; 44880</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12563; 32451</t>
+          <t>13139; 32963</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28993; 47072</t>
+          <t>29336; 46689</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40727</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>41427</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>73239</t>
+          <t>88360</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13345; 29833</t>
+          <t>13128; 30420</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20734; 42775</t>
+          <t>21041; 43258</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14418; 32796</t>
+          <t>14284; 33864</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29479; 58985</t>
+          <t>33222; 62211</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16629; 37114</t>
+          <t>18054; 38439</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11824; 29770</t>
+          <t>11711; 31052</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17766; 40925</t>
+          <t>16984; 39340</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15025; 48219</t>
+          <t>31883; 53071</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>35273; 62832</t>
+          <t>34342; 60237</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35548; 64504</t>
+          <t>37200; 66020</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36100; 67420</t>
+          <t>36166; 64992</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>44866; 93973</t>
+          <t>72042; 109096</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29124</t>
+          <t>32230</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>20697</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>49821</t>
+          <t>55868</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>26762; 50144</t>
+          <t>27152; 51136</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10631; 27744</t>
+          <t>10951; 29263</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24284; 47421</t>
+          <t>24138; 47354</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13493; 43508</t>
+          <t>24006; 44023</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>22961; 47929</t>
+          <t>24144; 48279</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17685; 37696</t>
+          <t>17070; 37738</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22721; 45794</t>
+          <t>21260; 45310</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14696; 28603</t>
+          <t>17130; 31811</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56541; 89873</t>
+          <t>55644; 87402</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>32365; 58314</t>
+          <t>31089; 57908</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>50556; 84530</t>
+          <t>52637; 84170</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>28424; 63370</t>
+          <t>44656; 69962</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>176960</t>
+          <t>190965</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>147595</t>
+          <t>163028</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>324555</t>
+          <t>353993</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>128507; 175060</t>
+          <t>128162; 176137</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>111254; 153947</t>
+          <t>111168; 157690</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105577; 150123</t>
+          <t>106988; 151519</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>132194; 204021</t>
+          <t>166361; 216189</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>105205; 150696</t>
+          <t>106550; 149062</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>126734; 174749</t>
+          <t>125933; 174392</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>134252; 187856</t>
+          <t>134684; 187085</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>124331; 172075</t>
+          <t>143315; 183498</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>244433; 310370</t>
+          <t>246647; 309740</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>248326; 314820</t>
+          <t>250073; 315456</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>255287; 322397</t>
+          <t>255624; 324470</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>279511; 363416</t>
+          <t>323764; 388032</t>
         </is>
       </c>
     </row>
